--- a/JOBWORK.xlsx
+++ b/JOBWORK.xlsx
@@ -15,21 +15,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="13">
-  <si>
-    <t>QUALITY</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="15">
+  <si>
+    <t>SUFI (GOLD)</t>
   </si>
   <si>
     <t>BEAM NO</t>
   </si>
   <si>
-    <t>METERS</t>
-  </si>
-  <si>
-    <t>SUFI (GOLD)</t>
-  </si>
-  <si>
-    <t>GRAND TOTAL</t>
+    <t>SENT MTR</t>
+  </si>
+  <si>
+    <t>DATE REC.</t>
+  </si>
+  <si>
+    <t>REC. MTR</t>
+  </si>
+  <si>
+    <t>TOTAL SENT</t>
+  </si>
+  <si>
+    <t>PENDING</t>
   </si>
   <si>
     <t>SUFI (SILVER)</t>
@@ -60,7 +66,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,8 +85,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -92,12 +109,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -120,30 +149,28 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -440,18 +467,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -461,154 +488,242 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>176</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>5000</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="4">
+        <v>46107</v>
+      </c>
+      <c r="E2" s="3">
+        <v>7925</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J2" s="4">
+        <v>46157</v>
+      </c>
+      <c r="K2" s="3">
+        <v>3942</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>177</v>
+      </c>
+      <c r="C3" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46119</v>
+      </c>
+      <c r="E3" s="3">
+        <v>8032</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J3" s="4">
+        <v>46157</v>
+      </c>
+      <c r="K3" s="3">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3">
+        <v>179</v>
+      </c>
+      <c r="C4" s="3">
+        <v>5400</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46127</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1309</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J4" s="4">
+        <v>46170</v>
+      </c>
+      <c r="K4" s="3">
+        <v>5834</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="3">
+        <v>180</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5400</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46127</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3524</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="3">
+        <v>7490</v>
+      </c>
+      <c r="J5" s="4">
+        <v>46170</v>
+      </c>
+      <c r="K5" s="3">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3">
+        <v>181</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5400</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46146</v>
+      </c>
+      <c r="E6" s="3">
+        <v>6519</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="3">
+        <v>7490</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3">
+        <v>199</v>
+      </c>
+      <c r="C7" s="3">
+        <v>6300</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46146</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5767</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="3">
+        <v>7490</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="B8" s="5">
         <v>6</v>
       </c>
-      <c r="G2" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2">
-        <v>177</v>
-      </c>
-      <c r="C3" s="2">
-        <v>5000</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="C8" s="5">
+        <v>32500</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="5">
+        <v>-576</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2">
-        <v>179</v>
-      </c>
-      <c r="C4" s="2">
-        <v>5400</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2">
-        <v>180</v>
-      </c>
-      <c r="C5" s="2">
-        <v>5400</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2">
-        <v>181</v>
-      </c>
-      <c r="C6" s="2">
-        <v>5400</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2">
-        <v>199</v>
-      </c>
-      <c r="C7" s="2">
-        <v>6300</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="H8" s="5">
         <v>6</v>
       </c>
-      <c r="C8" s="3">
-        <v>32500</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="I8" s="5">
+        <v>44970</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="3">
-        <v>44970</v>
+      <c r="K8" s="6">
+        <v>31206</v>
       </c>
     </row>
   </sheetData>
@@ -618,17 +733,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -636,258 +751,446 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3">
         <v>160</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="D2" s="4">
+        <v>46103</v>
+      </c>
+      <c r="E2" s="3">
+        <v>4513</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3">
         <v>161</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="D3" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3">
         <v>162</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="D4" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3">
         <v>164</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="D5" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3">
         <v>165</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="D6" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E6" s="3">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3">
         <v>183</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="D7" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3">
         <v>184</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="D8" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3">
         <v>200</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="D9" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3">
         <v>201</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="D10" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="3">
         <v>207</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="D11" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
         <v>215</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>5000</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="D12" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3">
         <v>218</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2">
+      <c r="D13" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3">
         <v>229</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="D14" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3">
         <v>230</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2">
+      <c r="D15" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
         <v>247</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>7550</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="D16" s="4">
+        <v>46137</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3">
         <v>250</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="2">
+      <c r="D17" s="4">
+        <v>46141</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3">
         <v>251</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="D18" s="4">
+        <v>46149</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3">
         <v>256</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <v>5300</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="2">
+      <c r="D19" s="4">
+        <v>46159</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="3">
         <v>262</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="2">
+      <c r="D20" s="4">
+        <v>46164</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3">
         <v>269</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="2">
+      <c r="D21" s="4">
+        <v>46164</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="3">
         <v>271</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="2">
+      <c r="D22" s="4">
+        <v>46165</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="3">
         <v>278</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="3">
+      <c r="D23" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="4">
+        <v>46178</v>
+      </c>
+      <c r="E25" s="3">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4">
+        <v>46182</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4">
+        <v>46185</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4283</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" s="5">
         <v>22</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C28" s="5">
         <v>146300</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="6">
+        <v>84220</v>
       </c>
     </row>
   </sheetData>

--- a/JOBWORK.xlsx
+++ b/JOBWORK.xlsx
@@ -15,21 +15,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="13">
-  <si>
-    <t>QUALITY</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="15">
+  <si>
+    <t>SUFI (GOLD)</t>
   </si>
   <si>
     <t>BEAM NO</t>
   </si>
   <si>
-    <t>METERS</t>
-  </si>
-  <si>
-    <t>SUFI (GOLD)</t>
-  </si>
-  <si>
-    <t>GRAND TOTAL</t>
+    <t>SENT MTR</t>
+  </si>
+  <si>
+    <t>DATE REC.</t>
+  </si>
+  <si>
+    <t>REC. MTR</t>
+  </si>
+  <si>
+    <t>TOTAL SENT</t>
+  </si>
+  <si>
+    <t>PENDING</t>
   </si>
   <si>
     <t>SUFI (SILVER)</t>
@@ -60,7 +66,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,8 +85,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -92,12 +109,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -120,30 +149,28 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -440,18 +467,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -461,154 +488,242 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>176</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>5000</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="4">
+        <v>46107</v>
+      </c>
+      <c r="E2" s="3">
+        <v>7925</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J2" s="4">
+        <v>46157</v>
+      </c>
+      <c r="K2" s="3">
+        <v>3942</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>177</v>
+      </c>
+      <c r="C3" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46119</v>
+      </c>
+      <c r="E3" s="3">
+        <v>8032</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J3" s="4">
+        <v>46157</v>
+      </c>
+      <c r="K3" s="3">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3">
+        <v>179</v>
+      </c>
+      <c r="C4" s="3">
+        <v>5400</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46127</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1309</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J4" s="4">
+        <v>46170</v>
+      </c>
+      <c r="K4" s="3">
+        <v>5834</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="3">
+        <v>180</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5400</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46127</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3524</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="3">
+        <v>7490</v>
+      </c>
+      <c r="J5" s="4">
+        <v>46170</v>
+      </c>
+      <c r="K5" s="3">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3">
+        <v>181</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5400</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46146</v>
+      </c>
+      <c r="E6" s="3">
+        <v>6519</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="3">
+        <v>7490</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3">
+        <v>199</v>
+      </c>
+      <c r="C7" s="3">
+        <v>6300</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46146</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5767</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="3">
+        <v>7490</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="B8" s="5">
         <v>6</v>
       </c>
-      <c r="G2" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2">
-        <v>177</v>
-      </c>
-      <c r="C3" s="2">
-        <v>5000</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="C8" s="5">
+        <v>32500</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="5">
+        <v>-576</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2">
-        <v>179</v>
-      </c>
-      <c r="C4" s="2">
-        <v>5400</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2">
-        <v>180</v>
-      </c>
-      <c r="C5" s="2">
-        <v>5400</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2">
-        <v>181</v>
-      </c>
-      <c r="C6" s="2">
-        <v>5400</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2">
-        <v>199</v>
-      </c>
-      <c r="C7" s="2">
-        <v>6300</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="H8" s="5">
         <v>6</v>
       </c>
-      <c r="C8" s="3">
-        <v>32500</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="I8" s="5">
+        <v>44970</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="3">
-        <v>44970</v>
+      <c r="K8" s="6">
+        <v>31206</v>
       </c>
     </row>
   </sheetData>
@@ -618,17 +733,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -636,258 +751,468 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3">
         <v>160</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="D2" s="4">
+        <v>46103</v>
+      </c>
+      <c r="E2" s="3">
+        <v>4513</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3">
         <v>161</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="D3" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3">
         <v>162</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="D4" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3">
         <v>164</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="D5" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3">
         <v>165</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="D6" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E6" s="3">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3">
         <v>183</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="D7" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3">
         <v>184</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="D8" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3">
         <v>200</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="D9" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3">
         <v>201</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="D10" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="3">
         <v>207</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="D11" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
         <v>215</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>5000</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="D12" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3">
         <v>218</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2">
+      <c r="D13" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3">
         <v>229</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="D14" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3">
         <v>230</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2">
+      <c r="D15" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
         <v>247</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>7550</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="D16" s="4">
+        <v>46137</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3">
         <v>250</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="2">
+      <c r="D17" s="4">
+        <v>46141</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3">
         <v>251</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="D18" s="4">
+        <v>46149</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3">
         <v>256</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <v>5300</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="2">
+      <c r="D19" s="4">
+        <v>46159</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="3">
         <v>262</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="2">
+      <c r="D20" s="4">
+        <v>46164</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3">
         <v>269</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="2">
+      <c r="D21" s="4">
+        <v>46164</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="3">
         <v>271</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="2">
+      <c r="D22" s="4">
+        <v>46165</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="3">
         <v>278</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="3">
+      <c r="D23" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="4">
+        <v>46178</v>
+      </c>
+      <c r="E25" s="3">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4">
+        <v>46182</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4">
+        <v>46185</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4283</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4">
+        <v>46186</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4">
+        <v>46186</v>
+      </c>
+      <c r="E29" s="3">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="5">
         <v>22</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C30" s="5">
         <v>146300</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="6">
+        <v>81682</v>
       </c>
     </row>
   </sheetData>

--- a/JOBWORK.xlsx
+++ b/JOBWORK.xlsx
@@ -15,21 +15,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="13">
-  <si>
-    <t>QUALITY</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="15">
+  <si>
+    <t>SUFI (GOLD)</t>
   </si>
   <si>
     <t>BEAM NO</t>
   </si>
   <si>
-    <t>METERS</t>
-  </si>
-  <si>
-    <t>SUFI (GOLD)</t>
-  </si>
-  <si>
-    <t>GRAND TOTAL</t>
+    <t>SENT MTR</t>
+  </si>
+  <si>
+    <t>DATE REC.</t>
+  </si>
+  <si>
+    <t>REC. MTR</t>
+  </si>
+  <si>
+    <t>TOTAL SENT</t>
+  </si>
+  <si>
+    <t>PENDING</t>
   </si>
   <si>
     <t>SUFI (SILVER)</t>
@@ -60,7 +66,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,8 +85,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -92,12 +109,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -120,30 +149,28 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -440,18 +467,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -461,154 +488,246 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>176</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>5000</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="4">
+        <v>46107</v>
+      </c>
+      <c r="E2" s="3">
+        <v>7925</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J2" s="4">
+        <v>46157</v>
+      </c>
+      <c r="K2" s="3">
+        <v>3942</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>177</v>
+      </c>
+      <c r="C3" s="3">
+        <v>5000</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46119</v>
+      </c>
+      <c r="E3" s="3">
+        <v>8032</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J3" s="4">
+        <v>46157</v>
+      </c>
+      <c r="K3" s="3">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3">
+        <v>179</v>
+      </c>
+      <c r="C4" s="3">
+        <v>5400</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46127</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1309</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J4" s="4">
+        <v>46170</v>
+      </c>
+      <c r="K4" s="3">
+        <v>5834</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="3">
+        <v>180</v>
+      </c>
+      <c r="C5" s="3">
+        <v>5400</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46127</v>
+      </c>
+      <c r="E5" s="3">
+        <v>3524</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="3">
+        <v>7490</v>
+      </c>
+      <c r="J5" s="4">
+        <v>46170</v>
+      </c>
+      <c r="K5" s="3">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3">
+        <v>181</v>
+      </c>
+      <c r="C6" s="3">
+        <v>5400</v>
+      </c>
+      <c r="D6" s="4">
+        <v>46146</v>
+      </c>
+      <c r="E6" s="3">
+        <v>6519</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="3">
+        <v>7490</v>
+      </c>
+      <c r="J6" s="4">
+        <v>46188</v>
+      </c>
+      <c r="K6" s="3">
+        <v>11804</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3">
+        <v>199</v>
+      </c>
+      <c r="C7" s="3">
+        <v>6300</v>
+      </c>
+      <c r="D7" s="4">
+        <v>46146</v>
+      </c>
+      <c r="E7" s="3">
+        <v>5767</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I7" s="3">
+        <v>7490</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="B8" s="5">
         <v>6</v>
       </c>
-      <c r="G2" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2">
-        <v>177</v>
-      </c>
-      <c r="C3" s="2">
-        <v>5000</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="C8" s="5">
+        <v>32500</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="5">
+        <v>-576</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2">
-        <v>179</v>
-      </c>
-      <c r="C4" s="2">
-        <v>5400</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2">
-        <v>180</v>
-      </c>
-      <c r="C5" s="2">
-        <v>5400</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2">
-        <v>181</v>
-      </c>
-      <c r="C6" s="2">
-        <v>5400</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2">
-        <v>199</v>
-      </c>
-      <c r="C7" s="2">
-        <v>6300</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="H8" s="5">
         <v>6</v>
       </c>
-      <c r="C8" s="3">
-        <v>32500</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="I8" s="5">
+        <v>44970</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="3">
-        <v>44970</v>
+      <c r="K8" s="6">
+        <v>19402</v>
       </c>
     </row>
   </sheetData>
@@ -618,17 +737,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -636,258 +755,590 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3">
         <v>160</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="D2" s="4">
+        <v>46103</v>
+      </c>
+      <c r="E2" s="3">
+        <v>4513</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3">
         <v>161</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="D3" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3">
         <v>162</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="D4" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3">
         <v>164</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="D5" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3">
         <v>165</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="D6" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E6" s="3">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3">
         <v>183</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="D7" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3">
         <v>184</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="D8" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3">
         <v>200</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="D9" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3">
         <v>201</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="D10" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="3">
         <v>207</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="D11" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3">
         <v>215</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>5000</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="D12" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3">
         <v>218</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2">
+      <c r="D13" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3">
         <v>229</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="D14" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3">
         <v>230</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2">
+      <c r="D15" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3">
         <v>247</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>7550</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="D16" s="4">
+        <v>46137</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3">
         <v>250</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="2">
+      <c r="D17" s="4">
+        <v>46141</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3">
         <v>251</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="D18" s="4">
+        <v>46149</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3">
         <v>256</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <v>5300</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" s="2">
+      <c r="D19" s="4">
+        <v>46159</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="3">
         <v>262</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" s="2">
+      <c r="D20" s="4">
+        <v>46164</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3">
         <v>269</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="2">
+      <c r="D21" s="4">
+        <v>46164</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="3">
         <v>271</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="2">
+      <c r="D22" s="4">
+        <v>46165</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="3">
         <v>278</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B24" s="3">
-        <v>22</v>
+        <v>288</v>
       </c>
       <c r="C24" s="3">
-        <v>146300</v>
+        <v>6800</v>
+      </c>
+      <c r="D24" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="3">
+        <v>289</v>
+      </c>
+      <c r="C25" s="3">
+        <v>6800</v>
+      </c>
+      <c r="D25" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4">
+        <v>46178</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4">
+        <v>46182</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4">
+        <v>46185</v>
+      </c>
+      <c r="E29" s="3">
+        <v>4283</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4">
+        <v>46186</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="4">
+        <v>46186</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="4">
+        <v>46188</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="4">
+        <v>46192</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4">
+        <v>46192</v>
+      </c>
+      <c r="E34" s="3">
+        <v>2986</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="4">
+        <v>46194</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4">
+        <v>46194</v>
+      </c>
+      <c r="E36" s="3">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="4">
+        <v>46197</v>
+      </c>
+      <c r="E37" s="3">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="4">
+        <v>46197</v>
+      </c>
+      <c r="E38" s="3">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="4">
+        <v>46199</v>
+      </c>
+      <c r="E39" s="3">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="5">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>159900</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="6">
+        <v>72018</v>
       </c>
     </row>
   </sheetData>

--- a/JOBWORK.xlsx
+++ b/JOBWORK.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="14">
   <si>
     <t>QUALITY</t>
   </si>
@@ -26,10 +26,13 @@
     <t>METERS</t>
   </si>
   <si>
+    <t>FLUTE</t>
+  </si>
+  <si>
+    <t>GRAND TOTAL</t>
+  </si>
+  <si>
     <t>SUFI (GOLD)</t>
-  </si>
-  <si>
-    <t>GRAND TOTAL</t>
   </si>
   <si>
     <t>SUFI (SILVER)</t>
@@ -440,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -449,9 +452,12 @@
     <col min="5" max="5" width="18.7109375" customWidth="1"/>
     <col min="6" max="7" width="12.7109375" customWidth="1"/>
     <col min="8" max="8" width="3.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
+    <col min="10" max="11" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,137 +476,164 @@
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="I1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2">
-        <v>176</v>
+        <v>274</v>
       </c>
       <c r="C2" s="2">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="2">
+        <v>176</v>
+      </c>
+      <c r="G2" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2">
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2">
         <v>7500</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:11">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>177</v>
+        <v>276</v>
       </c>
       <c r="C3" s="2">
-        <v>5000</v>
+        <v>9700</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>7</v>
+      <c r="F3" s="2">
+        <v>177</v>
       </c>
       <c r="G3" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="2">
         <v>7500</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2">
-        <v>179</v>
-      </c>
-      <c r="C4" s="2">
-        <v>5400</v>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>15200</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
+      <c r="F4" s="2">
+        <v>179</v>
       </c>
       <c r="G4" s="2">
+        <v>5400</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="2">
         <v>7500</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2">
-        <v>180</v>
-      </c>
-      <c r="C5" s="2">
-        <v>5400</v>
-      </c>
+    <row r="5" spans="1:11">
       <c r="E5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>9</v>
+      <c r="F5" s="2">
+        <v>180</v>
       </c>
       <c r="G5" s="2">
+        <v>5400</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="2">
         <v>7490</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2">
-        <v>181</v>
-      </c>
-      <c r="C6" s="2">
-        <v>5400</v>
-      </c>
+    <row r="6" spans="1:11">
       <c r="E6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
+      <c r="F6" s="2">
+        <v>181</v>
       </c>
       <c r="G6" s="2">
+        <v>5400</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="2">
         <v>7490</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2">
-        <v>199</v>
-      </c>
-      <c r="C7" s="2">
-        <v>6300</v>
-      </c>
+    <row r="7" spans="1:11">
       <c r="E7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>11</v>
+      <c r="F7" s="2">
+        <v>199</v>
       </c>
       <c r="G7" s="2">
+        <v>6300</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7" s="2">
         <v>7490</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3">
-        <v>6</v>
-      </c>
-      <c r="C8" s="3">
-        <v>32500</v>
-      </c>
+    <row r="8" spans="1:11">
       <c r="E8" s="3" t="s">
         <v>4</v>
       </c>
@@ -608,6 +641,15 @@
         <v>6</v>
       </c>
       <c r="G8" s="3">
+        <v>32500</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J8" s="3">
+        <v>6</v>
+      </c>
+      <c r="K8" s="3">
         <v>44970</v>
       </c>
     </row>
@@ -639,7 +681,7 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2">
         <v>160</v>
@@ -650,7 +692,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2">
         <v>161</v>
@@ -661,7 +703,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2">
         <v>162</v>
@@ -672,7 +714,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2">
         <v>164</v>
@@ -683,7 +725,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
         <v>165</v>
@@ -694,7 +736,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2">
         <v>183</v>
@@ -705,7 +747,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2">
         <v>184</v>
@@ -716,7 +758,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2">
         <v>200</v>
@@ -727,7 +769,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2">
         <v>201</v>
@@ -738,7 +780,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2">
         <v>207</v>
@@ -749,7 +791,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2">
         <v>215</v>
@@ -760,7 +802,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2">
         <v>218</v>
@@ -771,7 +813,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2">
         <v>229</v>
@@ -782,7 +824,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2">
         <v>230</v>
@@ -793,7 +835,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" s="2">
         <v>247</v>
@@ -804,7 +846,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2">
         <v>250</v>
@@ -815,7 +857,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2">
         <v>251</v>
@@ -826,7 +868,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" s="2">
         <v>256</v>
@@ -837,7 +879,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2">
         <v>262</v>
@@ -848,7 +890,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B21" s="2">
         <v>269</v>
@@ -859,7 +901,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B22" s="2">
         <v>271</v>
@@ -870,7 +912,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2">
         <v>278</v>
@@ -881,7 +923,7 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B24" s="2">
         <v>288</v>
@@ -892,7 +934,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B25" s="2">
         <v>289</v>

--- a/JOBWORK.xlsx
+++ b/JOBWORK.xlsx
@@ -15,21 +15,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="14">
-  <si>
-    <t>QUALITY</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="16">
+  <si>
+    <t>FLUTE</t>
   </si>
   <si>
     <t>BEAM NO</t>
   </si>
   <si>
-    <t>METERS</t>
-  </si>
-  <si>
-    <t>FLUTE</t>
-  </si>
-  <si>
-    <t>GRAND TOTAL</t>
+    <t>SENT MTR</t>
+  </si>
+  <si>
+    <t>DATE REC.</t>
+  </si>
+  <si>
+    <t>REC. MTR</t>
+  </si>
+  <si>
+    <t>TOTAL SENT</t>
+  </si>
+  <si>
+    <t>PENDING</t>
   </si>
   <si>
     <t>SUFI (GOLD)</t>
@@ -63,7 +69,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,8 +88,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -95,12 +112,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -123,30 +152,28 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -443,21 +470,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="3.7109375" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="11" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="11" width="12.7109375" customWidth="1"/>
     <col min="12" max="12" width="3.7109375" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="17" width="12.7109375" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -467,190 +494,298 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="B2" s="3">
+        <v>274</v>
+      </c>
+      <c r="C2" s="3">
+        <v>5500</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3">
+        <v>176</v>
+      </c>
+      <c r="I2" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J2" s="4">
+        <v>46107</v>
+      </c>
+      <c r="K2" s="3">
+        <v>7925</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="3">
+        <v>7500</v>
+      </c>
+      <c r="P2" s="4">
+        <v>46157</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>3942</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>276</v>
+      </c>
+      <c r="C3" s="3">
+        <v>9700</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="3">
+        <v>177</v>
+      </c>
+      <c r="I3" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J3" s="4">
+        <v>46119</v>
+      </c>
+      <c r="K3" s="3">
+        <v>8032</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" s="3">
+        <v>7500</v>
+      </c>
+      <c r="P3" s="4">
+        <v>46157</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2">
-        <v>274</v>
-      </c>
-      <c r="C2" s="2">
-        <v>5500</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C4" s="5">
+        <v>15200</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="6">
+        <v>15200</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="3">
+        <v>179</v>
+      </c>
+      <c r="I4" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J4" s="4">
+        <v>46127</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1309</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="3">
+        <v>7500</v>
+      </c>
+      <c r="P4" s="4">
+        <v>46170</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>5834</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="G5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="3">
+        <v>180</v>
+      </c>
+      <c r="I5" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J5" s="4">
+        <v>46127</v>
+      </c>
+      <c r="K5" s="3">
+        <v>3524</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O5" s="3">
+        <v>7490</v>
+      </c>
+      <c r="P5" s="4">
+        <v>46170</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="G6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="3">
+        <v>181</v>
+      </c>
+      <c r="I6" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J6" s="4">
+        <v>46146</v>
+      </c>
+      <c r="K6" s="3">
+        <v>6519</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O6" s="3">
+        <v>7490</v>
+      </c>
+      <c r="P6" s="4">
+        <v>46188</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>11804</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="G7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="3">
+        <v>199</v>
+      </c>
+      <c r="I7" s="3">
+        <v>6300</v>
+      </c>
+      <c r="J7" s="4">
+        <v>46146</v>
+      </c>
+      <c r="K7" s="3">
+        <v>5767</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O7" s="3">
+        <v>7490</v>
+      </c>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="G8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2">
-        <v>176</v>
-      </c>
-      <c r="G2" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="H8" s="5">
         <v>6</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2">
-        <v>276</v>
-      </c>
-      <c r="C3" s="2">
-        <v>9700</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="I8" s="5">
+        <v>32500</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="5">
+        <v>-576</v>
+      </c>
+      <c r="M8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2">
-        <v>177</v>
-      </c>
-      <c r="G3" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="N8" s="5">
         <v>6</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3">
-        <v>15200</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2">
-        <v>179</v>
-      </c>
-      <c r="G4" s="2">
-        <v>5400</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="O8" s="5">
+        <v>44970</v>
+      </c>
+      <c r="P8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="E5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2">
-        <v>180</v>
-      </c>
-      <c r="G5" s="2">
-        <v>5400</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2">
-        <v>181</v>
-      </c>
-      <c r="G6" s="2">
-        <v>5400</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K6" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="E7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2">
-        <v>199</v>
-      </c>
-      <c r="G7" s="2">
-        <v>6300</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K7" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3">
-        <v>6</v>
-      </c>
-      <c r="G8" s="3">
-        <v>32500</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3">
-        <v>6</v>
-      </c>
-      <c r="K8" s="3">
-        <v>44970</v>
+      <c r="Q8" s="6">
+        <v>19402</v>
       </c>
     </row>
   </sheetData>
@@ -660,17 +795,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -678,280 +813,590 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="3">
         <v>160</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="D2" s="4">
+        <v>46103</v>
+      </c>
+      <c r="E2" s="3">
+        <v>4513</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3">
         <v>161</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="D3" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3">
         <v>162</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="D4" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3">
         <v>164</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="D5" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3">
         <v>165</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="D6" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E6" s="3">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3">
         <v>183</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="D7" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="3">
         <v>184</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="D8" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="3">
         <v>200</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="D9" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="3">
         <v>201</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="D10" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="3">
         <v>207</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="D11" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="3">
         <v>215</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>5000</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="D12" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="3">
         <v>218</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2">
+      <c r="D13" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3">
         <v>229</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="D14" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3">
         <v>230</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="2">
+      <c r="D15" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3">
         <v>247</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>7550</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="D16" s="4">
+        <v>46137</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3">
         <v>250</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="2">
+      <c r="D17" s="4">
+        <v>46141</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3">
         <v>251</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="D18" s="4">
+        <v>46149</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3">
         <v>256</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <v>5300</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="2">
+      <c r="D19" s="4">
+        <v>46159</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="3">
         <v>262</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="2">
+      <c r="D20" s="4">
+        <v>46164</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="3">
         <v>269</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="2">
+      <c r="D21" s="4">
+        <v>46164</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="3">
         <v>271</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="2">
+      <c r="D22" s="4">
+        <v>46165</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="3">
         <v>278</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="2">
+      <c r="D23" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="3">
         <v>288</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="2">
+      <c r="D24" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="3">
         <v>289</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="3">
+      <c r="D25" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4">
+        <v>46178</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4">
+        <v>46182</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4">
+        <v>46185</v>
+      </c>
+      <c r="E29" s="3">
+        <v>4283</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4">
+        <v>46186</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="4">
+        <v>46186</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="4">
+        <v>46188</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="4">
+        <v>46192</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4">
+        <v>46192</v>
+      </c>
+      <c r="E34" s="3">
+        <v>2986</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="4">
+        <v>46194</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4">
+        <v>46194</v>
+      </c>
+      <c r="E36" s="3">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="4">
+        <v>46197</v>
+      </c>
+      <c r="E37" s="3">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="4">
+        <v>46197</v>
+      </c>
+      <c r="E38" s="3">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="4">
+        <v>46199</v>
+      </c>
+      <c r="E39" s="3">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="5">
         <v>24</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C40" s="5">
         <v>159900</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="6">
+        <v>72018</v>
       </c>
     </row>
   </sheetData>

--- a/JOBWORK.xlsx
+++ b/JOBWORK.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="16">
   <si>
     <t>FLUTE</t>
   </si>
@@ -1199,7 +1199,7 @@
         <v>15</v>
       </c>
       <c r="B24" s="3">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C24" s="3">
         <v>6800</v>
@@ -1216,7 +1216,7 @@
         <v>15</v>
       </c>
       <c r="B25" s="3">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C25" s="3">
         <v>6800</v>
@@ -1229,9 +1229,15 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="3">
+        <v>288</v>
+      </c>
+      <c r="C26" s="3">
+        <v>6800</v>
+      </c>
       <c r="D26" s="4">
         <v>46177</v>
       </c>
@@ -1240,9 +1246,15 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+      <c r="A27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="3">
+        <v>289</v>
+      </c>
+      <c r="C27" s="3">
+        <v>6800</v>
+      </c>
       <c r="D27" s="4">
         <v>46178</v>
       </c>
@@ -1251,9 +1263,15 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
+      <c r="A28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="3">
+        <v>296</v>
+      </c>
+      <c r="C28" s="3">
+        <v>6800</v>
+      </c>
       <c r="D28" s="4">
         <v>46182</v>
       </c>
@@ -1262,9 +1280,15 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
+      <c r="A29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="3">
+        <v>297</v>
+      </c>
+      <c r="C29" s="3">
+        <v>6800</v>
+      </c>
       <c r="D29" s="4">
         <v>46185</v>
       </c>
@@ -1387,16 +1411,16 @@
         <v>5</v>
       </c>
       <c r="B40" s="5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C40" s="5">
-        <v>159900</v>
+        <v>187100</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E40" s="6">
-        <v>72018</v>
+        <v>99218</v>
       </c>
     </row>
   </sheetData>

--- a/JOBWORK.xlsx
+++ b/JOBWORK.xlsx
@@ -15,21 +15,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="16">
   <si>
-    <t>QUALITY</t>
+    <t>FLUTE</t>
   </si>
   <si>
     <t>BEAM NO</t>
   </si>
   <si>
-    <t>METERS</t>
+    <t>SENT MTR</t>
   </si>
   <si>
-    <t>FLUTE</t>
+    <t>DATE REC.</t>
   </si>
   <si>
-    <t>GRAND TOTAL</t>
+    <t>REC. MTR</t>
+  </si>
+  <si>
+    <t>TOTAL SENT</t>
+  </si>
+  <si>
+    <t>PENDING</t>
   </si>
   <si>
     <t>SUFI (GOLD)</t>
@@ -63,7 +69,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,8 +88,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -95,12 +112,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -123,30 +152,28 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -443,21 +470,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
-    <col min="6" max="7" width="12.7109375" customWidth="1"/>
-    <col min="8" max="8" width="3.7109375" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
-    <col min="10" max="11" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="11" width="12.7109375" customWidth="1"/>
     <col min="12" max="12" width="3.7109375" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="17" width="12.7109375" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -467,190 +494,309 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="B2" s="3">
+        <v>274</v>
+      </c>
+      <c r="C2" s="3">
+        <v>5500</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3">
+        <v>176</v>
+      </c>
+      <c r="I2" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J2" s="4">
+        <v>46107</v>
+      </c>
+      <c r="K2" s="3">
+        <v>7925</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="3">
+        <v>7500</v>
+      </c>
+      <c r="P2" s="4">
+        <v>46157</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>3942</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>276</v>
+      </c>
+      <c r="C3" s="3">
+        <v>9700</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="3">
+        <v>177</v>
+      </c>
+      <c r="I3" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J3" s="4">
+        <v>46119</v>
+      </c>
+      <c r="K3" s="3">
+        <v>8032</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" s="3">
+        <v>7500</v>
+      </c>
+      <c r="P3" s="4">
+        <v>46157</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="5">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2">
-        <v>274</v>
-      </c>
-      <c r="C2" s="2">
-        <v>5500</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C4" s="5">
+        <v>15200</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="6">
+        <v>15200</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="3">
+        <v>179</v>
+      </c>
+      <c r="I4" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J4" s="4">
+        <v>46127</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1309</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="3">
+        <v>7500</v>
+      </c>
+      <c r="P4" s="4">
+        <v>46170</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>5834</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="G5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="3">
+        <v>180</v>
+      </c>
+      <c r="I5" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J5" s="4">
+        <v>46127</v>
+      </c>
+      <c r="K5" s="3">
+        <v>3524</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O5" s="3">
+        <v>7490</v>
+      </c>
+      <c r="P5" s="4">
+        <v>46170</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>2187</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="G6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" s="3">
+        <v>181</v>
+      </c>
+      <c r="I6" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J6" s="4">
+        <v>46146</v>
+      </c>
+      <c r="K6" s="3">
+        <v>6519</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O6" s="3">
+        <v>7490</v>
+      </c>
+      <c r="P6" s="4">
+        <v>46188</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>11804</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="G7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" s="3">
+        <v>199</v>
+      </c>
+      <c r="I7" s="3">
+        <v>6300</v>
+      </c>
+      <c r="J7" s="4">
+        <v>46146</v>
+      </c>
+      <c r="K7" s="3">
+        <v>5767</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O7" s="3">
+        <v>7490</v>
+      </c>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="4">
+        <v>46198</v>
+      </c>
+      <c r="K8" s="3">
+        <v>6553</v>
+      </c>
+      <c r="M8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2">
-        <v>176</v>
-      </c>
-      <c r="G2" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="N8" s="5">
         <v>6</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K2" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2">
-        <v>276</v>
-      </c>
-      <c r="C3" s="2">
-        <v>9700</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="O8" s="5">
+        <v>44970</v>
+      </c>
+      <c r="P8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>19402</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="G9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2">
-        <v>177</v>
-      </c>
-      <c r="G3" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="H9" s="5">
         <v>6</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3">
-        <v>15200</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2">
-        <v>179</v>
-      </c>
-      <c r="G4" s="2">
-        <v>5400</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="I9" s="5">
+        <v>32500</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="2">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="E5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2">
-        <v>180</v>
-      </c>
-      <c r="G5" s="2">
-        <v>5400</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="K5" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2">
-        <v>181</v>
-      </c>
-      <c r="G6" s="2">
-        <v>5400</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K6" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="E7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="2">
-        <v>199</v>
-      </c>
-      <c r="G7" s="2">
-        <v>6300</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K7" s="2">
-        <v>7490</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3">
-        <v>6</v>
-      </c>
-      <c r="G8" s="3">
-        <v>32500</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="3">
-        <v>6</v>
-      </c>
-      <c r="K8" s="3">
-        <v>44970</v>
+      <c r="K9" s="5">
+        <v>-7129</v>
       </c>
     </row>
   </sheetData>
@@ -660,17 +806,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -678,324 +824,691 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="2">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="3">
         <v>160</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="D2" s="4">
+        <v>46103</v>
+      </c>
+      <c r="E2" s="3">
+        <v>4513</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3">
         <v>161</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2">
+      <c r="D3" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1603</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3">
         <v>162</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="D4" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1604</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3">
         <v>164</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2">
+      <c r="D5" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1612</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3">
         <v>165</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="D6" s="4">
+        <v>46114</v>
+      </c>
+      <c r="E6" s="3">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="3">
         <v>183</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="D7" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="3">
         <v>184</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="D8" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="3">
         <v>200</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="D9" s="4">
+        <v>46120</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2515</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="3">
         <v>201</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="D10" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="3">
         <v>207</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="D11" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1830</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="3">
         <v>215</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="3">
         <v>5000</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="D12" s="4">
+        <v>46126</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1808</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="3">
         <v>218</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2">
+      <c r="D13" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E13" s="3">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3">
         <v>229</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="D14" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2404</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3">
         <v>230</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="2">
+      <c r="D15" s="4">
+        <v>46131</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3">
         <v>247</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>7550</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2">
+      <c r="D16" s="4">
+        <v>46137</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2503</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="3">
         <v>250</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="2">
+      <c r="D17" s="4">
+        <v>46141</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3">
         <v>251</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="2">
+      <c r="D18" s="4">
+        <v>46149</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3">
         <v>256</v>
       </c>
-      <c r="C19" s="2">
+      <c r="C19" s="3">
         <v>5300</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="2">
+      <c r="D19" s="4">
+        <v>46159</v>
+      </c>
+      <c r="E19" s="3">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="3">
         <v>262</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <v>6750</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="2">
+      <c r="D20" s="4">
+        <v>46164</v>
+      </c>
+      <c r="E20" s="3">
+        <v>2504</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="3">
         <v>269</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21" s="3">
         <v>5600</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="2">
+      <c r="D21" s="4">
+        <v>46164</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2505</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="3">
         <v>271</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22" s="3">
         <v>7600</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="2">
+      <c r="D22" s="4">
+        <v>46165</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2521</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="3">
         <v>278</v>
       </c>
-      <c r="C23" s="2">
+      <c r="C23" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="2">
+      <c r="D23" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2702</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="3">
         <v>280</v>
       </c>
-      <c r="C24" s="2">
+      <c r="C24" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="2">
+      <c r="D24" s="4">
+        <v>46170</v>
+      </c>
+      <c r="E24" s="3">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="3">
         <v>281</v>
       </c>
-      <c r="C25" s="2">
+      <c r="C25" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="2">
+      <c r="D25" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2534</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="3">
         <v>288</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="2">
+      <c r="D26" s="4">
+        <v>46177</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2514</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="3">
         <v>289</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="2">
+      <c r="D27" s="4">
+        <v>46178</v>
+      </c>
+      <c r="E27" s="3">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="3">
         <v>296</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="2">
+      <c r="D28" s="4">
+        <v>46182</v>
+      </c>
+      <c r="E28" s="3">
+        <v>2682</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="3">
         <v>297</v>
       </c>
-      <c r="C29" s="2">
+      <c r="C29" s="3">
         <v>6800</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="3">
+      <c r="D29" s="4">
+        <v>46185</v>
+      </c>
+      <c r="E29" s="3">
+        <v>4283</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4">
+        <v>46186</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1502</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="4">
+        <v>46186</v>
+      </c>
+      <c r="E31" s="3">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="4">
+        <v>46188</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1826</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="4">
+        <v>46192</v>
+      </c>
+      <c r="E33" s="3">
+        <v>2865</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4">
+        <v>46192</v>
+      </c>
+      <c r="E34" s="3">
+        <v>2986</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="4">
+        <v>46194</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2574</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4">
+        <v>46194</v>
+      </c>
+      <c r="E36" s="3">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="4">
+        <v>46197</v>
+      </c>
+      <c r="E37" s="3">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="4">
+        <v>46197</v>
+      </c>
+      <c r="E38" s="3">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="4">
+        <v>46199</v>
+      </c>
+      <c r="E39" s="3">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4">
+        <v>46202</v>
+      </c>
+      <c r="E40" s="3">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="4">
+        <v>46203</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="4">
+        <v>46206</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="4">
+        <v>46206</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="4">
+        <v>46207</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="4">
+        <v>46209</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="4">
+        <v>46209</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="5">
         <v>28</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C47" s="5">
         <v>187100</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E47" s="6">
+        <v>85852</v>
       </c>
     </row>
   </sheetData>

--- a/JOBWORK.xlsx
+++ b/JOBWORK.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="16">
   <si>
     <t>FLUTE</t>
   </si>
@@ -1308,9 +1308,15 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
+      <c r="A30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="3">
+        <v>309</v>
+      </c>
+      <c r="C30" s="3">
+        <v>6800</v>
+      </c>
       <c r="D30" s="4">
         <v>46186</v>
       </c>
@@ -1319,9 +1325,15 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+      <c r="A31" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="3">
+        <v>310</v>
+      </c>
+      <c r="C31" s="3">
+        <v>6800</v>
+      </c>
       <c r="D31" s="4">
         <v>46186</v>
       </c>
@@ -1499,16 +1511,16 @@
         <v>5</v>
       </c>
       <c r="B47" s="5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C47" s="5">
-        <v>187100</v>
+        <v>200700</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>6</v>
       </c>
       <c r="E47" s="6">
-        <v>85852</v>
+        <v>99452</v>
       </c>
     </row>
   </sheetData>
